--- a/docs/templates/fg-slob-template.xlsx
+++ b/docs/templates/fg-slob-template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -435,8 +435,9 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,10 +478,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Case Rate (USD)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>SLOB Category</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
